--- a/我的课表.xlsx
+++ b/我的课表.xlsx
@@ -211,7 +211,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-4周,6-18周</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-2周,4周,6-18周</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -383,7 +383,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-4周,6-18周</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-2周,4周,6-18周</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-2周,4-5周,7-18周</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-4周,6-18周</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-2周,4-5周,7-18周</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -962,17 +962,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CB1101716-B</t>
+          <t>CB1101716-A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>物理中的数学模型1-B</t>
+          <t>物理中的数学模型1-A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -985,32 +985,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>4周</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期日</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>第三双节第1小节10:45-11:30</t>
+          <t>第五双节第1单节15:45-16:30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>第三双节第2小节11:31-12:15</t>
+          <t>第五双节第2单节16:31-17:15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ZAKHAROVA IRINA</t>
+          <t>SHCHEGLOV ALEXEY</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2-116</t>
+          <t>3-107</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1036,29 +1036,29 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2021级数学2班</t>
+          <t>2021级数学1班,2021级数学2班,2021级数学3班</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>讨论</t>
+          <t>讲座</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CB1101718</t>
+          <t>CB1101716-B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>最优化方法</t>
+          <t>物理中的数学模型1-B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1071,42 +1071,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-2周,6-18周</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期二</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>第一单节08:00-08:45</t>
+          <t>第三双节第1小节10:45-11:30</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>第二双节第2小节09:46-10:30</t>
+          <t>第三双节第2小节11:31-12:15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BUDAK BORIS</t>
+          <t>ZAKHAROVA IRINA</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3-107</t>
+          <t>2-116</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>选修</t>
+          <t>必修</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>专业选修</t>
+          <t>专业必修</t>
         </is>
       </c>
       <c r="N12"/>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2021级数学1班,2021级数学2班,2021级数学3班</t>
+          <t>2021级数学2班</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>讲座</t>
+          <t>讨论</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-2周,4-5周,7-18周</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>第一单节08:00-08:45</t>
+          <t>第二双节第2小节09:46-10:30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1220,17 +1220,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CB1101781</t>
+          <t>CB1101718</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外语5</t>
+          <t>最优化方法</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1239,46 +1239,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-4周,6-18周</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>星期一</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>第五双节第1单节15:45-16:30</t>
+          <t>第一单节08:00-08:45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>第五双节第2单节16:31-17:15</t>
+          <t>第一单节08:00-08:45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NOSOVA MARIIA</t>
+          <t>BUDAK BORIS</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1-408</t>
+          <t>3-107</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>必修</t>
+          <t>选修</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>公共必修</t>
+          <t>专业选修</t>
         </is>
       </c>
       <c r="N14"/>
@@ -1294,24 +1294,24 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2021级数学2班</t>
+          <t>2021级数学1班,2021级数学2班,2021级数学3班</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>讨论</t>
+          <t>讲座</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CB1101782</t>
+          <t>CB1101781</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>专业交流外语5</t>
+          <t>外语5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1325,31 +1325,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>7-18周</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>星期三</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>第二双节第1小节09:00-09:45</t>
+          <t>第五双节第1单节15:45-16:30</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>第二双节第2小节09:46-10:30</t>
+          <t>第五双节第2单节16:31-17:15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>KOLOBAEVA LIIA</t>
+          <t>PASHKOVSKAIA SVETLANA</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1392,12 +1392,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CB1101782</t>
+          <t>CB1101781</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>专业交流外语5</t>
+          <t>外语5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,36 +1411,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-2周,4-5周</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>星期四</t>
+          <t>星期一</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>第三双节第1小节10:45-11:30</t>
+          <t>第五双节第1单节15:45-16:30</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>第三双节第2小节11:31-12:15</t>
+          <t>第五双节第2单节16:31-17:15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>KOLOBAEVA LIIA</t>
+          <t>NOSOVA MARIIA</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2-116</t>
+          <t>1-408</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1478,17 +1478,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CB1101821</t>
+          <t>CB1101782</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>分布式数据处理</t>
+          <t>专业交流外语5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1497,36 +1497,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>1-4周</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>星期二</t>
+          <t>星期三</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>第四双节第1小节14:00-14:45</t>
+          <t>第二双节第1小节09:00-09:45</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>第四双节第2小节14:46-15:30</t>
+          <t>第二双节第2小节09:46-10:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>DEMIN ALEKSEI</t>
+          <t>KOLOBAEVA LIIA</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2-116</t>
+          <t>1-408</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>专业必修</t>
+          <t>公共必修</t>
         </is>
       </c>
       <c r="N17"/>
@@ -1552,29 +1552,29 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2021级数学1班,2021级数学2班,2021级数学3班</t>
+          <t>2021级数学2班</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>讲座</t>
+          <t>讨论</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CB1101821</t>
+          <t>CB1101782</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>分布式数据处理</t>
+          <t>专业交流外语5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01S02</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1583,11 +1583,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1-18周</t>
+          <t>6-18周</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1597,22 +1597,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>第六双节第1单节18:00-18:45</t>
+          <t>第二双节第1小节09:00-09:45</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>第六双节第2单节18:46-19:30</t>
+          <t>第二双节第2小节09:46-10:30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>DEMIN ALEKSEI</t>
+          <t>PASHKOVSKAIA SVETLANA</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1-111</t>
+          <t>1-408</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>专业必修</t>
+          <t>公共必修</t>
         </is>
       </c>
       <c r="N18"/>
@@ -1643,24 +1643,24 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>实践</t>
+          <t>讨论</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CB1101834</t>
+          <t>CB1101782</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>控制论的数学基础</t>
+          <t>专业交流外语5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1669,16 +1669,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1-4周,6-18周</t>
+          <t>6-18周</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>星期五</t>
+          <t>星期四</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ZAKHAROV VLADIMIR</t>
+          <t>PASHKOVSKAIA SVETLANA</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3-107</t>
+          <t>2-116</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>专业必修</t>
+          <t>公共必修</t>
         </is>
       </c>
       <c r="N19"/>
@@ -1724,10 +1724,526 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>2021级数学2班</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>讨论</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CB1101782</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>专业交流外语5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>计算数学与控制系-1101</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1-4周</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>第三双节第1小节10:45-11:30</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>第三双节第2小节11:31-12:15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>KOLOBAEVA LIIA</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2-116</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>必修</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>公共必修</t>
+        </is>
+      </c>
+      <c r="N20"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>本校区</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>面授教学</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2021级数学2班</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>讨论</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CB1101821</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>分布式数据处理</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>计算数学与控制系-1101</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1-2周,4周,6-18周</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>第四双节第1小节14:00-14:45</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>第四双节第2小节14:46-15:30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DEMIN ALEKSEI</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2-116</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>必修</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>专业必修</t>
+        </is>
+      </c>
+      <c r="N21"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>本校区</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>面授教学</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>2021级数学1班,2021级数学2班,2021级数学3班</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>讲座</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CB1101821</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>分布式数据处理</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>01S02</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>计算数学与控制系-1101</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1-4周,6-18周</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>第六双节第1单节18:00-18:45</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>第六双节第2单节18:46-19:30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DEMIN ALEKSEI</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1-111</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>必修</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>专业必修</t>
+        </is>
+      </c>
+      <c r="N22"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>本校区</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>面授教学</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2021级数学2班</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>实践</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CB1101834</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>控制论的数学基础</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>计算数学与控制系-1101</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1-2周,4周,6-18周</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>第三双节第1小节10:45-11:30</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>第三双节第2小节11:31-12:15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ZAKHAROV VLADIMIR</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2A-201</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>必修</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>专业必修</t>
+        </is>
+      </c>
+      <c r="N23"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>本校区</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>面授教学</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2021级数学1班,2021级数学2班,2021级数学3班</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>讲座</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CB1101834</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>控制论的数学基础</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>计算数学与控制系-1101</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>6周</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>第三双节第1小节10:45-11:30</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>第三双节第2小节11:31-12:15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ZAKHAROV VLADIMIR</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1-113</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>必修</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>专业必修</t>
+        </is>
+      </c>
+      <c r="N24"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>本校区</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>面授教学</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2021级数学1班,2021级数学2班,2021级数学3班</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>讲座</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CB1101834</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>控制论的数学基础</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>计算数学与控制系-1101</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4周</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>星期日</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>第三双节第1小节10:45-11:30</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>第三双节第2小节11:31-12:15</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ZAKHAROV VLADIMIR</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2A-201</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>必修</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>专业必修</t>
+        </is>
+      </c>
+      <c r="N25"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>本校区</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>面授教学</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2021级数学1班,2021级数学2班,2021级数学3班</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>讲座</t>
         </is>
